--- a/testData/Opencart_LoginDataFile.xlsx
+++ b/testData/Opencart_LoginDataFile.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VICKY\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VICKY\eclipse-workspace\OpencartStore\testData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5C4F2AD1-9579-423F-95E6-4953C64AE999}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3621CFDD-86E6-4303-920D-E52AED6A12B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1F2D179E-37D2-4BC0-88A9-F5C135B87DA5}"/>
+    <workbookView xWindow="1500" yWindow="1500" windowWidth="17280" windowHeight="8964" xr2:uid="{1F2D179E-37D2-4BC0-88A9-F5C135B87DA5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,21 +20,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="17">
   <si>
     <t>username</t>
   </si>
@@ -82,6 +73,9 @@
   </si>
   <si>
     <t>TUSHAR2717</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -196,7 +190,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -514,7 +508,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{884FCF78-0A3E-40BF-9E26-11C478AF56E2}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="37.21875" customWidth="1"/>
@@ -522,7 +516,7 @@
     <col min="3" max="3" width="18.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="21" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -533,7 +527,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="21" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:5" ht="21" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
@@ -544,7 +538,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="21" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:5" ht="21" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -555,7 +549,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="21" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:5" ht="21" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
@@ -566,7 +560,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="21" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:5" ht="21" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
@@ -577,7 +571,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="21" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:5" ht="21" x14ac:dyDescent="0.4">
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
@@ -588,7 +582,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="21" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:5" ht="21" x14ac:dyDescent="0.4">
       <c r="A7" s="5" t="s">
         <v>14</v>
       </c>
@@ -597,6 +591,11 @@
       </c>
       <c r="C7" s="6" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E9" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
